--- a/src/烟草进价零售价毛利表.xlsx
+++ b/src/烟草进价零售价毛利表.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="烟草进价零售价毛利表" sheetId="1" r:id="rId1"/>
     <sheet name="说明" sheetId="2" r:id="rId2"/>
+    <sheet name="段位总量" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -16022,4 +16023,428 @@
     <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AE4"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" customWidth="1"/>
+    <col min="6" max="6" width="6.83203125" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" customWidth="1"/>
+    <col min="10" max="10" width="6.83203125" customWidth="1"/>
+    <col min="11" max="11" width="6.83203125" customWidth="1"/>
+    <col min="12" max="12" width="6.83203125" customWidth="1"/>
+    <col min="13" max="13" width="6.83203125" customWidth="1"/>
+    <col min="14" max="14" width="6.83203125" customWidth="1"/>
+    <col min="15" max="15" width="6.83203125" customWidth="1"/>
+    <col min="16" max="16" width="6.83203125" customWidth="1"/>
+    <col min="17" max="17" width="6.83203125" customWidth="1"/>
+    <col min="18" max="18" width="6.83203125" customWidth="1"/>
+    <col min="19" max="19" width="6.83203125" customWidth="1"/>
+    <col min="20" max="20" width="6.83203125" customWidth="1"/>
+    <col min="21" max="21" width="6.83203125" customWidth="1"/>
+    <col min="22" max="22" width="6.83203125" customWidth="1"/>
+    <col min="23" max="23" width="6.83203125" customWidth="1"/>
+    <col min="24" max="24" width="6.83203125" customWidth="1"/>
+    <col min="25" max="25" width="6.83203125" customWidth="1"/>
+    <col min="26" max="26" width="6.83203125" customWidth="1"/>
+    <col min="27" max="27" width="6.83203125" customWidth="1"/>
+    <col min="28" max="28" width="6.83203125" customWidth="1"/>
+    <col min="29" max="29" width="6.83203125" customWidth="1"/>
+    <col min="30" max="30" width="6.83203125" customWidth="1"/>
+    <col min="31" max="31" width="6.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>段位</v>
+      </c>
+      <c r="B1" t="str">
+        <v>30档</v>
+      </c>
+      <c r="C1" t="str">
+        <v>29档</v>
+      </c>
+      <c r="D1" t="str">
+        <v>28档</v>
+      </c>
+      <c r="E1" t="str">
+        <v>27档</v>
+      </c>
+      <c r="F1" t="str">
+        <v>26档</v>
+      </c>
+      <c r="G1" t="str">
+        <v>25档</v>
+      </c>
+      <c r="H1" t="str">
+        <v>24档</v>
+      </c>
+      <c r="I1" t="str">
+        <v>23档</v>
+      </c>
+      <c r="J1" t="str">
+        <v>22档</v>
+      </c>
+      <c r="K1" t="str">
+        <v>21档</v>
+      </c>
+      <c r="L1" t="str">
+        <v>20档</v>
+      </c>
+      <c r="M1" t="str">
+        <v>19档</v>
+      </c>
+      <c r="N1" t="str">
+        <v>18档</v>
+      </c>
+      <c r="O1" t="str">
+        <v>17档</v>
+      </c>
+      <c r="P1" t="str">
+        <v>16档</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>15档</v>
+      </c>
+      <c r="R1" t="str">
+        <v>14档</v>
+      </c>
+      <c r="S1" t="str">
+        <v>13档</v>
+      </c>
+      <c r="T1" t="str">
+        <v>12档</v>
+      </c>
+      <c r="U1" t="str">
+        <v>11档</v>
+      </c>
+      <c r="V1" t="str">
+        <v>10档</v>
+      </c>
+      <c r="W1" t="str">
+        <v>09档</v>
+      </c>
+      <c r="X1" t="str">
+        <v>08档</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>07档</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>06档</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>05档</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>04档</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>03档</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>02档</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>01档</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>5段</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v/>
+      </c>
+      <c r="AB2" t="str">
+        <v/>
+      </c>
+      <c r="AC2" t="str">
+        <v/>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>6段</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>7段</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="P4">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE4"/>
+  </ignoredErrors>
+</worksheet>
 </file>